--- a/data/df_tesoro.xlsx
+++ b/data/df_tesoro.xlsx
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O744"/>
+  <dimension ref="A1:O747"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -35391,6 +35391,147 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="745" spans="1:15">
+      <c r="A745" s="2">
+        <v>46014</v>
+      </c>
+      <c r="B745">
+        <v>3.71</v>
+      </c>
+      <c r="C745">
+        <v>3.7</v>
+      </c>
+      <c r="D745">
+        <v>3.65</v>
+      </c>
+      <c r="E745">
+        <v>3.66</v>
+      </c>
+      <c r="F745">
+        <v>3.59</v>
+      </c>
+      <c r="G745">
+        <v>3.52</v>
+      </c>
+      <c r="H745">
+        <v>3.48</v>
+      </c>
+      <c r="I745">
+        <v>3.58</v>
+      </c>
+      <c r="J745">
+        <v>3.72</v>
+      </c>
+      <c r="K745">
+        <v>3.94</v>
+      </c>
+      <c r="L745">
+        <v>4.18</v>
+      </c>
+      <c r="M745">
+        <v>4.78</v>
+      </c>
+      <c r="N745">
+        <v>4.83</v>
+      </c>
+      <c r="O745">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="746" spans="1:15">
+      <c r="A746" s="2">
+        <v>46015</v>
+      </c>
+      <c r="B746">
+        <v>3.72</v>
+      </c>
+      <c r="C746">
+        <v>3.74</v>
+      </c>
+      <c r="D746">
+        <v>3.69</v>
+      </c>
+      <c r="E746">
+        <v>3.67</v>
+      </c>
+      <c r="F746">
+        <v>3.59</v>
+      </c>
+      <c r="G746">
+        <v>3.5</v>
+      </c>
+      <c r="H746">
+        <v>3.47</v>
+      </c>
+      <c r="I746">
+        <v>3.56</v>
+      </c>
+      <c r="J746">
+        <v>3.7</v>
+      </c>
+      <c r="K746">
+        <v>3.91</v>
+      </c>
+      <c r="L746">
+        <v>4.15</v>
+      </c>
+      <c r="M746">
+        <v>4.75</v>
+      </c>
+      <c r="N746">
+        <v>4.79</v>
+      </c>
+      <c r="O746">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15">
+      <c r="A747" s="2">
+        <v>46017</v>
+      </c>
+      <c r="B747">
+        <v>3.7</v>
+      </c>
+      <c r="C747">
+        <v>3.72</v>
+      </c>
+      <c r="D747">
+        <v>3.64</v>
+      </c>
+      <c r="E747">
+        <v>3.66</v>
+      </c>
+      <c r="F747">
+        <v>3.58</v>
+      </c>
+      <c r="G747">
+        <v>3.49</v>
+      </c>
+      <c r="H747">
+        <v>3.46</v>
+      </c>
+      <c r="I747">
+        <v>3.54</v>
+      </c>
+      <c r="J747">
+        <v>3.68</v>
+      </c>
+      <c r="K747">
+        <v>3.89</v>
+      </c>
+      <c r="L747">
+        <v>4.14</v>
+      </c>
+      <c r="M747">
+        <v>4.76</v>
+      </c>
+      <c r="N747">
+        <v>4.81</v>
+      </c>
+      <c r="O747">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
